--- a/结果/大纲分析报告.xlsx
+++ b/结果/大纲分析报告.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>难度(平均得分率)</t>
+          <t>平均得分</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -461,13 +461,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>0.656</v>
+        <v>15.75</v>
       </c>
       <c r="E2" t="n">
         <v>0.656</v>
       </c>
       <c r="F2" t="n">
-        <v>0.906</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.602</v>
+        <v>3.611</v>
       </c>
       <c r="E3" t="n">
         <v>0.602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.656</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +511,7 @@
         <v>0.589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.327</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="5">
@@ -527,13 +527,13 @@
         <v>69</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>51.744</v>
       </c>
       <c r="E5" t="n">
         <v>0.75</v>
       </c>
       <c r="F5" t="n">
-        <v>0.95</v>
+        <v>0.237</v>
       </c>
     </row>
   </sheetData>
